--- a/pz-analysis/PZ_Nigeria_Analysis.xlsx
+++ b/pz-analysis/PZ_Nigeria_Analysis.xlsx
@@ -24,77 +24,48 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="5">
     <font>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <sz val="10"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="16"/>
+      <color rgb="00000000"/>
+      <sz val="14"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <i val="1"/>
-      <color rgb="00404040"/>
-      <sz val="10"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001F3864"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00404040"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="000000FF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00404040"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -103,30 +74,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
-        <bgColor rgb="001F3864"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-        <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DEEBF7"/>
-        <bgColor rgb="00DEEBF7"/>
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -136,39 +89,25 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00000000"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00000000"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="medium">
-        <color rgb="001F3864"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00000000"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -177,109 +116,42 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -367,19 +239,19 @@
           <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
-              <a:defRPr sz="1200" b="1">
+              <a:defRPr sz="1400" b="0">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="595959"/>
                 </a:solidFill>
-                <a:latin typeface="Arial"/>
+                <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr sz="1200" b="1">
+              <a:rPr sz="1400" b="0">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="595959"/>
                 </a:solidFill>
-                <a:latin typeface="Arial"/>
+                <a:latin typeface="+mn-lt"/>
               </a:rPr>
               <a:t>Average PESTLE Score by Factor (out of 25)</a:t>
             </a:r>
@@ -421,21 +293,21 @@
             <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
             <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
-                <a:defRPr sz="900" b="1">
+                <a:defRPr sz="900" b="0">
                   <a:solidFill>
-                    <a:srgbClr val="000000"/>
+                    <a:srgbClr val="404040"/>
                   </a:solidFill>
-                  <a:latin typeface="Arial"/>
+                  <a:latin typeface="+mn-lt"/>
                 </a:defRPr>
               </a:pPr>
               <a:r>
                 <a:t/>
               </a:r>
-              <a:endParaRPr sz="900" b="1">
+              <a:endParaRPr sz="900" b="0">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="404040"/>
                 </a:solidFill>
-                <a:latin typeface="Arial"/>
+                <a:latin typeface="+mn-lt"/>
               </a:endParaRPr>
             </a:p>
           </txPr>
@@ -446,7 +318,7 @@
           <showSerName val="0"/>
           <showPercent val="0"/>
         </dLbls>
-        <gapWidth val="60"/>
+        <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -462,7 +334,7 @@
         <spPr>
           <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
             <a:solidFill>
-              <a:srgbClr val="A6A6A6"/>
+              <a:srgbClr val="D9D9D9"/>
             </a:solidFill>
             <a:prstDash val="solid"/>
           </a:ln>
@@ -473,9 +345,9 @@
             <a:pPr>
               <a:defRPr sz="900" b="0">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="595959"/>
                 </a:solidFill>
-                <a:latin typeface="Arial"/>
+                <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
@@ -483,9 +355,9 @@
             </a:r>
             <a:endParaRPr sz="900" b="0">
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:srgbClr val="595959"/>
               </a:solidFill>
-              <a:latin typeface="Arial"/>
+              <a:latin typeface="+mn-lt"/>
             </a:endParaRPr>
           </a:p>
         </txPr>
@@ -524,21 +396,21 @@
           <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
-              <a:defRPr sz="800" b="0">
+              <a:defRPr sz="900" b="0">
                 <a:solidFill>
-                  <a:srgbClr val="404040"/>
+                  <a:srgbClr val="595959"/>
                 </a:solidFill>
-                <a:latin typeface="Arial"/>
+                <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="800" b="0">
+            <a:endParaRPr sz="900" b="0">
               <a:solidFill>
-                <a:srgbClr val="404040"/>
+                <a:srgbClr val="595959"/>
               </a:solidFill>
-              <a:latin typeface="Arial"/>
+              <a:latin typeface="+mn-lt"/>
             </a:endParaRPr>
           </a:p>
         </txPr>
@@ -552,7 +424,7 @@
   <spPr>
     <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
       <a:solidFill>
-        <a:srgbClr val="BFBFBF"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -569,19 +441,19 @@
           <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
-              <a:defRPr sz="1200" b="1">
+              <a:defRPr sz="1400" b="0">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="595959"/>
                 </a:solidFill>
-                <a:latin typeface="Arial"/>
+                <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr sz="1200" b="1">
+              <a:rPr sz="1400" b="0">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="595959"/>
                 </a:solidFill>
-                <a:latin typeface="Arial"/>
+                <a:latin typeface="+mn-lt"/>
               </a:rPr>
               <a:t>Weighted SWOT Scores</a:t>
             </a:r>
@@ -623,21 +495,21 @@
             <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
             <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
-                <a:defRPr sz="900" b="1">
+                <a:defRPr sz="900" b="0">
                   <a:solidFill>
-                    <a:srgbClr val="000000"/>
+                    <a:srgbClr val="404040"/>
                   </a:solidFill>
-                  <a:latin typeface="Arial"/>
+                  <a:latin typeface="+mn-lt"/>
                 </a:defRPr>
               </a:pPr>
               <a:r>
                 <a:t/>
               </a:r>
-              <a:endParaRPr sz="900" b="1">
+              <a:endParaRPr sz="900" b="0">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="404040"/>
                 </a:solidFill>
-                <a:latin typeface="Arial"/>
+                <a:latin typeface="+mn-lt"/>
               </a:endParaRPr>
             </a:p>
           </txPr>
@@ -648,7 +520,7 @@
           <showSerName val="0"/>
           <showPercent val="0"/>
         </dLbls>
-        <gapWidth val="60"/>
+        <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -664,7 +536,7 @@
         <spPr>
           <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
             <a:solidFill>
-              <a:srgbClr val="A6A6A6"/>
+              <a:srgbClr val="D9D9D9"/>
             </a:solidFill>
             <a:prstDash val="solid"/>
           </a:ln>
@@ -675,9 +547,9 @@
             <a:pPr>
               <a:defRPr sz="900" b="0">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="595959"/>
                 </a:solidFill>
-                <a:latin typeface="Arial"/>
+                <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
@@ -685,9 +557,9 @@
             </a:r>
             <a:endParaRPr sz="900" b="0">
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:srgbClr val="595959"/>
               </a:solidFill>
-              <a:latin typeface="Arial"/>
+              <a:latin typeface="+mn-lt"/>
             </a:endParaRPr>
           </a:p>
         </txPr>
@@ -726,21 +598,21 @@
           <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
-              <a:defRPr sz="800" b="0">
+              <a:defRPr sz="900" b="0">
                 <a:solidFill>
-                  <a:srgbClr val="404040"/>
+                  <a:srgbClr val="595959"/>
                 </a:solidFill>
-                <a:latin typeface="Arial"/>
+                <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="800" b="0">
+            <a:endParaRPr sz="900" b="0">
               <a:solidFill>
-                <a:srgbClr val="404040"/>
+                <a:srgbClr val="595959"/>
               </a:solidFill>
-              <a:latin typeface="Arial"/>
+              <a:latin typeface="+mn-lt"/>
             </a:endParaRPr>
           </a:p>
         </txPr>
@@ -754,7 +626,7 @@
   <spPr>
     <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
       <a:solidFill>
-        <a:srgbClr val="BFBFBF"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -771,19 +643,19 @@
           <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
-              <a:defRPr sz="1200" b="1">
+              <a:defRPr sz="1400" b="0">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="595959"/>
                 </a:solidFill>
-                <a:latin typeface="Arial"/>
+                <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr sz="1200" b="1">
+              <a:rPr sz="1400" b="0">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="595959"/>
                 </a:solidFill>
-                <a:latin typeface="Arial"/>
+                <a:latin typeface="+mn-lt"/>
               </a:rPr>
               <a:t>Porter's Five Forces: Strength (1 to 5)</a:t>
             </a:r>
@@ -825,21 +697,21 @@
             <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
             <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
-                <a:defRPr sz="900" b="1">
+                <a:defRPr sz="900" b="0">
                   <a:solidFill>
-                    <a:srgbClr val="000000"/>
+                    <a:srgbClr val="404040"/>
                   </a:solidFill>
-                  <a:latin typeface="Arial"/>
+                  <a:latin typeface="+mn-lt"/>
                 </a:defRPr>
               </a:pPr>
               <a:r>
                 <a:t/>
               </a:r>
-              <a:endParaRPr sz="900" b="1">
+              <a:endParaRPr sz="900" b="0">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="404040"/>
                 </a:solidFill>
-                <a:latin typeface="Arial"/>
+                <a:latin typeface="+mn-lt"/>
               </a:endParaRPr>
             </a:p>
           </txPr>
@@ -850,7 +722,7 @@
           <showSerName val="0"/>
           <showPercent val="0"/>
         </dLbls>
-        <gapWidth val="60"/>
+        <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -866,7 +738,7 @@
         <spPr>
           <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
             <a:solidFill>
-              <a:srgbClr val="A6A6A6"/>
+              <a:srgbClr val="D9D9D9"/>
             </a:solidFill>
             <a:prstDash val="solid"/>
           </a:ln>
@@ -877,9 +749,9 @@
             <a:pPr>
               <a:defRPr sz="900" b="0">
                 <a:solidFill>
-                  <a:srgbClr val="000000"/>
+                  <a:srgbClr val="595959"/>
                 </a:solidFill>
-                <a:latin typeface="Arial"/>
+                <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
@@ -887,9 +759,9 @@
             </a:r>
             <a:endParaRPr sz="900" b="0">
               <a:solidFill>
-                <a:srgbClr val="000000"/>
+                <a:srgbClr val="595959"/>
               </a:solidFill>
-              <a:latin typeface="Arial"/>
+              <a:latin typeface="+mn-lt"/>
             </a:endParaRPr>
           </a:p>
         </txPr>
@@ -928,21 +800,21 @@
           <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
-              <a:defRPr sz="800" b="0">
+              <a:defRPr sz="900" b="0">
                 <a:solidFill>
-                  <a:srgbClr val="404040"/>
+                  <a:srgbClr val="595959"/>
                 </a:solidFill>
-                <a:latin typeface="Arial"/>
+                <a:latin typeface="+mn-lt"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:t/>
             </a:r>
-            <a:endParaRPr sz="800" b="0">
+            <a:endParaRPr sz="900" b="0">
               <a:solidFill>
-                <a:srgbClr val="404040"/>
+                <a:srgbClr val="595959"/>
               </a:solidFill>
-              <a:latin typeface="Arial"/>
+              <a:latin typeface="+mn-lt"/>
             </a:endParaRPr>
           </a:p>
         </txPr>
@@ -956,7 +828,7 @@
   <spPr>
     <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
       <a:solidFill>
-        <a:srgbClr val="BFBFBF"/>
+        <a:srgbClr val="D9D9D9"/>
       </a:solidFill>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -1056,104 +928,46 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1165,173 +979,148 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001F3864"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1342,7 +1131,7 @@
     <col width="96" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
+    <row r="1" ht="21" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>PZ NIGERIA LIMITED: COMPANY PROFILE</t>
@@ -1356,7 +1145,6 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="8" customHeight="1"/>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1382,12 +1170,12 @@
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Department</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Marketing Department, Ilupeju, Lagos</t>
         </is>
@@ -1406,12 +1194,12 @@
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Chief Financial Officer</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Mr Oladare Oresukan</t>
         </is>
@@ -1430,12 +1218,12 @@
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Electrical business</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Air conditioners, fridges and freezers, washing machines</t>
         </is>
@@ -1454,12 +1242,12 @@
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>How it is organised</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Product and brand structure: each brand has its own manager, and shared support teams serve all the brands</t>
         </is>
@@ -1477,78 +1265,77 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>What is in this workbook</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>PESTLE</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Political, Economic, Social, Technological, Legal and Environmental factors, each scored Impact × Likelihood, with a summary and chart per factor</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>SWOT</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Strengths, Weaknesses, Opportunities and Threats in a 2 × 2 matrix</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>SWOT Scoring</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>The SWOT points weighted and rated (IFE and EFE matrices) and the strategy they point to</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Industry Analysis</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Industry overview, Porter's Five Forces and the main competitors</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>The key results from every sheet, and the recommendations</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>Blue figures are inputs (ratings and weights) you can change. Black figures are formulas: change any blue figure and every score, summary, chart and conclusion updates.</t>
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>The ratings and weights are typed in; everything else is a formula. Change any rating or weight and every score, summary, chart and conclusion updates.</t>
         </is>
       </c>
     </row>
@@ -1560,23 +1347,14 @@
     <mergeCell ref="A15:B15"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;8 PZ Nigeria Limited - &amp;A - Page &amp;P of &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001F3864"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1587,13 +1365,13 @@
     <col width="36" customWidth="1" min="2" max="2"/>
     <col width="54" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
+    <row r="1" ht="21" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>PESTLE ANALYSIS: PZ NIGERIA LIMITED</t>
@@ -1607,7 +1385,6 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="8" customHeight="1"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1624,27 +1401,27 @@
           <t>Effect on PZ Nigeria</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Impact (1-5)</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Likelihood (1-5)</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="H4" s="13" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
@@ -1666,22 +1443,22 @@
           <t>Higher fuel and transport costs; easier access to dollars over time</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>Threat</t>
         </is>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="15" t="n">
+      <c r="F5" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="10">
         <f>E5*F5</f>
         <v>20</v>
       </c>
-      <c r="H5" s="14" t="str">
+      <c r="H5" s="9" t="str">
         <f>IF(G5&gt;=16,"High",IF(G5&gt;=9,"Medium","Low"))</f>
         <v>High</v>
       </c>
@@ -1702,22 +1479,22 @@
           <t>Imported raw materials and parts cost more</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>Threat</t>
         </is>
       </c>
-      <c r="E6" s="15" t="n">
+      <c r="E6" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="15" t="n">
+      <c r="F6" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="10">
         <f>E6*F6</f>
         <v>12</v>
       </c>
-      <c r="H6" s="14" t="str">
+      <c r="H6" s="9" t="str">
         <f>IF(G6&gt;=16,"High",IF(G6&gt;=9,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
@@ -1738,130 +1515,130 @@
           <t>Uncertainty can delay investment and change the rules</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>Threat</t>
         </is>
       </c>
-      <c r="E7" s="15" t="n">
+      <c r="E7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F7" s="15" t="n">
+      <c r="F7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="10">
         <f>E7*F7</f>
         <v>9</v>
       </c>
-      <c r="H7" s="14" t="str">
+      <c r="H7" s="9" t="str">
         <f>IF(G7&gt;=16,"High",IF(G7&gt;=9,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Economic</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Naira devaluation and FX shortages</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Imported raw materials cost much more; losses on foreign-currency debts</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>Threat</t>
         </is>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="F8" s="18" t="n">
+      <c r="F8" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="10">
         <f>E8*F8</f>
         <v>25</v>
       </c>
-      <c r="H8" s="17" t="str">
+      <c r="H8" s="9" t="str">
         <f>IF(G8&gt;=16,"High",IF(G8&gt;=9,"Medium","Low"))</f>
         <v>High</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Economic</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>High inflation</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Shoppers buy less or switch to cheaper brands</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>Threat</t>
         </is>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="F9" s="18" t="n">
+      <c r="F9" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="10">
         <f>E9*F9</f>
         <v>25</v>
       </c>
-      <c r="H9" s="17" t="str">
+      <c r="H9" s="9" t="str">
         <f>IF(G9&gt;=16,"High",IF(G9&gt;=9,"Medium","Low"))</f>
         <v>High</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Economic</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>High interest rates</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Borrowing is expensive; fewer appliances bought on credit</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>Threat</t>
         </is>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F10" s="18" t="n">
+      <c r="F10" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="10">
         <f>E10*F10</f>
         <v>12</v>
       </c>
-      <c r="H10" s="17" t="str">
+      <c r="H10" s="9" t="str">
         <f>IF(G10&gt;=16,"High",IF(G10&gt;=9,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
@@ -1882,22 +1659,22 @@
           <t>A big and growing market for soaps, detergents and appliances</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>Opportunity</t>
         </is>
       </c>
-      <c r="E11" s="15" t="n">
+      <c r="E11" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="15" t="n">
+      <c r="F11" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="10">
         <f>E11*F11</f>
         <v>20</v>
       </c>
-      <c r="H11" s="14" t="str">
+      <c r="H11" s="9" t="str">
         <f>IF(G11&gt;=16,"High",IF(G11&gt;=9,"Medium","Low"))</f>
         <v>High</v>
       </c>
@@ -1918,22 +1695,22 @@
           <t>Demand for smaller, cheaper packs</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>Opportunity</t>
         </is>
       </c>
-      <c r="E12" s="15" t="n">
+      <c r="E12" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="F12" s="15" t="n">
+      <c r="F12" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="10">
         <f>E12*F12</f>
         <v>16</v>
       </c>
-      <c r="H12" s="14" t="str">
+      <c r="H12" s="9" t="str">
         <f>IF(G12&gt;=16,"High",IF(G12&gt;=9,"Medium","Low"))</f>
         <v>High</v>
       </c>
@@ -1954,130 +1731,130 @@
           <t>More demand for soaps and cleaning products</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>Opportunity</t>
         </is>
       </c>
-      <c r="E13" s="15" t="n">
+      <c r="E13" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F13" s="15" t="n">
+      <c r="F13" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="10">
         <f>E13*F13</f>
         <v>12</v>
       </c>
-      <c r="H13" s="14" t="str">
+      <c r="H13" s="9" t="str">
         <f>IF(G13&gt;=16,"High",IF(G13&gt;=9,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Technological</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Social media and digital marketing</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Cheaper, targeted adverts that reach young buyers</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>Opportunity</t>
         </is>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F14" s="18" t="n">
+      <c r="F14" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="10">
         <f>E14*F14</f>
         <v>15</v>
       </c>
-      <c r="H14" s="17" t="str">
+      <c r="H14" s="9" t="str">
         <f>IF(G14&gt;=16,"High",IF(G14&gt;=9,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Technological</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>E-commerce and modern retail</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>New ways to sell: online stores and supermarkets</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>Opportunity</t>
         </is>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E15" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F15" s="18" t="n">
+      <c r="F15" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="10">
         <f>E15*F15</f>
         <v>12</v>
       </c>
-      <c r="H15" s="17" t="str">
+      <c r="H15" s="9" t="str">
         <f>IF(G15&gt;=16,"High",IF(G15&gt;=9,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Technological</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Poor power supply</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Factories spend more on diesel and solar; demand for energy-saving appliances</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>Threat</t>
         </is>
       </c>
-      <c r="E16" s="18" t="n">
+      <c r="E16" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="F16" s="18" t="n">
+      <c r="F16" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G16" s="19">
+      <c r="G16" s="10">
         <f>E16*F16</f>
         <v>16</v>
       </c>
-      <c r="H16" s="17" t="str">
+      <c r="H16" s="9" t="str">
         <f>IF(G16&gt;=16,"High",IF(G16&gt;=9,"Medium","Low"))</f>
         <v>High</v>
       </c>
@@ -2098,22 +1875,22 @@
           <t>Every product must be registered and meet standards</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>Threat</t>
         </is>
       </c>
-      <c r="E17" s="15" t="n">
+      <c r="E17" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F17" s="15" t="n">
+      <c r="F17" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="10">
         <f>E17*F17</f>
         <v>15</v>
       </c>
-      <c r="H17" s="14" t="str">
+      <c r="H17" s="9" t="str">
         <f>IF(G17&gt;=16,"High",IF(G17&gt;=9,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
@@ -2134,22 +1911,22 @@
           <t>Adverts need approval; fair prices and clear labels</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>Threat</t>
         </is>
       </c>
-      <c r="E18" s="15" t="n">
+      <c r="E18" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="F18" s="15" t="n">
+      <c r="F18" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="10">
         <f>E18*F18</f>
         <v>8</v>
       </c>
-      <c r="H18" s="14" t="str">
+      <c r="H18" s="9" t="str">
         <f>IF(G18&gt;=16,"High",IF(G18&gt;=9,"Medium","Low"))</f>
         <v>Low</v>
       </c>
@@ -2170,167 +1947,160 @@
           <t>Higher staff costs and new tax rules to follow</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>Threat</t>
         </is>
       </c>
-      <c r="E19" s="15" t="n">
+      <c r="E19" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F19" s="15" t="n">
+      <c r="F19" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="10">
         <f>E19*F19</f>
         <v>12</v>
       </c>
-      <c r="H19" s="14" t="str">
+      <c r="H19" s="9" t="str">
         <f>IF(G19&gt;=16,"High",IF(G19&gt;=9,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Environmental</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Plastic waste rules</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Must change packaging and pay for recycling (EPR)</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>Threat</t>
         </is>
       </c>
-      <c r="E20" s="18" t="n">
+      <c r="E20" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F20" s="18" t="n">
+      <c r="F20" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="10">
         <f>E20*F20</f>
         <v>12</v>
       </c>
-      <c r="H20" s="17" t="str">
+      <c r="H20" s="9" t="str">
         <f>IF(G20&gt;=16,"High",IF(G20&gt;=9,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Environmental</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Flooding and climate change</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Floods disrupt deliveries and damage stock</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>Threat</t>
         </is>
       </c>
-      <c r="E21" s="18" t="n">
+      <c r="E21" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F21" s="18" t="n">
+      <c r="F21" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="10">
         <f>E21*F21</f>
         <v>9</v>
       </c>
-      <c r="H21" s="17" t="str">
+      <c r="H21" s="9" t="str">
         <f>IF(G21&gt;=16,"High",IF(G21&gt;=9,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Environmental</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Demand for eco-friendly products</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>A chance to launch greener packs and appliances</t>
         </is>
       </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>Opportunity</t>
         </is>
       </c>
-      <c r="E22" s="18" t="n">
+      <c r="E22" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="18" t="n">
+      <c r="F22" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="G22" s="19">
+      <c r="G22" s="10">
         <f>E22*F22</f>
         <v>6</v>
       </c>
-      <c r="H22" s="17" t="str">
+      <c r="H22" s="9" t="str">
         <f>IF(G22&gt;=16,"High",IF(G22&gt;=9,"Medium","Low"))</f>
         <v>Low</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Average score (all issues)</t>
         </is>
       </c>
-      <c r="B23" s="21" t="n"/>
-      <c r="C23" s="21" t="n"/>
-      <c r="D23" s="21" t="n"/>
-      <c r="E23" s="21" t="n"/>
-      <c r="F23" s="21" t="n"/>
-      <c r="G23" s="22">
+      <c r="B23" s="11" t="n"/>
+      <c r="C23" s="11" t="n"/>
+      <c r="D23" s="11" t="n"/>
+      <c r="E23" s="11" t="n"/>
+      <c r="F23" s="11" t="n"/>
+      <c r="G23" s="12">
         <f>AVERAGE(G5:G22)</f>
         <v>14.2222222222222</v>
       </c>
-      <c r="H23" s="23" t="str">
+      <c r="H23" s="10" t="str">
         <f>IF(G23&gt;=16,"High",IF(G23&gt;=9,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
     </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>PESTLE summary by factor</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="9" t="n"/>
-      <c r="F25" s="9" t="n"/>
-      <c r="G25" s="9" t="n"/>
-      <c r="H25" s="9" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
@@ -2338,37 +2108,37 @@
           <t>Factor</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>Number of issues (COUNTIF)</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>Average score (AVERAGEIF)</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>Highest score</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>High priority</t>
         </is>
       </c>
-      <c r="F26" s="13" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>Threats</t>
         </is>
       </c>
-      <c r="G26" s="13" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>Opportunities</t>
         </is>
       </c>
-      <c r="H26" s="13" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
@@ -2380,66 +2150,66 @@
           <t>Political</t>
         </is>
       </c>
-      <c r="B27" s="14">
+      <c r="B27" s="9">
         <f>COUNTIF($A$5:$A$22,A27)</f>
         <v>3</v>
       </c>
-      <c r="C27" s="24">
+      <c r="C27" s="12">
         <f>AVERAGEIF($A$5:$A$22,A27,$G$5:$G$22)</f>
         <v>13.6666666666667</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="9">
         <f>SUMPRODUCT(MAX(($A$5:$A$22=A27)*$G$5:$G$22))</f>
         <v>20</v>
       </c>
-      <c r="E27" s="14">
+      <c r="E27" s="9">
         <f>COUNTIFS($A$5:$A$22,A27,$H$5:$H$22,"High")</f>
         <v>1</v>
       </c>
-      <c r="F27" s="14">
+      <c r="F27" s="9">
         <f>COUNTIFS($A$5:$A$22,A27,$D$5:$D$22,"Threat")</f>
         <v>3</v>
       </c>
-      <c r="G27" s="14">
+      <c r="G27" s="9">
         <f>COUNTIFS($A$5:$A$22,A27,$D$5:$D$22,"Opportunity")</f>
         <v>0</v>
       </c>
-      <c r="H27" s="14">
+      <c r="H27" s="9">
         <f>RANK(C27,$C$27:$C$32)</f>
         <v>4</v>
       </c>
     </row>
     <row r="28" ht="21" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Economic</t>
         </is>
       </c>
-      <c r="B28" s="17">
+      <c r="B28" s="9">
         <f>COUNTIF($A$5:$A$22,A28)</f>
         <v>3</v>
       </c>
-      <c r="C28" s="25">
+      <c r="C28" s="12">
         <f>AVERAGEIF($A$5:$A$22,A28,$G$5:$G$22)</f>
         <v>20.6666666666667</v>
       </c>
-      <c r="D28" s="17">
+      <c r="D28" s="9">
         <f>SUMPRODUCT(MAX(($A$5:$A$22=A28)*$G$5:$G$22))</f>
         <v>25</v>
       </c>
-      <c r="E28" s="17">
+      <c r="E28" s="9">
         <f>COUNTIFS($A$5:$A$22,A28,$H$5:$H$22,"High")</f>
         <v>2</v>
       </c>
-      <c r="F28" s="17">
+      <c r="F28" s="9">
         <f>COUNTIFS($A$5:$A$22,A28,$D$5:$D$22,"Threat")</f>
         <v>3</v>
       </c>
-      <c r="G28" s="17">
+      <c r="G28" s="9">
         <f>COUNTIFS($A$5:$A$22,A28,$D$5:$D$22,"Opportunity")</f>
         <v>0</v>
       </c>
-      <c r="H28" s="17">
+      <c r="H28" s="9">
         <f>RANK(C28,$C$27:$C$32)</f>
         <v>1</v>
       </c>
@@ -2450,66 +2220,66 @@
           <t>Social</t>
         </is>
       </c>
-      <c r="B29" s="14">
+      <c r="B29" s="9">
         <f>COUNTIF($A$5:$A$22,A29)</f>
         <v>3</v>
       </c>
-      <c r="C29" s="24">
+      <c r="C29" s="12">
         <f>AVERAGEIF($A$5:$A$22,A29,$G$5:$G$22)</f>
         <v>16</v>
       </c>
-      <c r="D29" s="14">
+      <c r="D29" s="9">
         <f>SUMPRODUCT(MAX(($A$5:$A$22=A29)*$G$5:$G$22))</f>
         <v>20</v>
       </c>
-      <c r="E29" s="14">
+      <c r="E29" s="9">
         <f>COUNTIFS($A$5:$A$22,A29,$H$5:$H$22,"High")</f>
         <v>2</v>
       </c>
-      <c r="F29" s="14">
+      <c r="F29" s="9">
         <f>COUNTIFS($A$5:$A$22,A29,$D$5:$D$22,"Threat")</f>
         <v>0</v>
       </c>
-      <c r="G29" s="14">
+      <c r="G29" s="9">
         <f>COUNTIFS($A$5:$A$22,A29,$D$5:$D$22,"Opportunity")</f>
         <v>3</v>
       </c>
-      <c r="H29" s="14">
+      <c r="H29" s="9">
         <f>RANK(C29,$C$27:$C$32)</f>
         <v>2</v>
       </c>
     </row>
     <row r="30" ht="21" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Technological</t>
         </is>
       </c>
-      <c r="B30" s="17">
+      <c r="B30" s="9">
         <f>COUNTIF($A$5:$A$22,A30)</f>
         <v>3</v>
       </c>
-      <c r="C30" s="25">
+      <c r="C30" s="12">
         <f>AVERAGEIF($A$5:$A$22,A30,$G$5:$G$22)</f>
         <v>14.3333333333333</v>
       </c>
-      <c r="D30" s="17">
+      <c r="D30" s="9">
         <f>SUMPRODUCT(MAX(($A$5:$A$22=A30)*$G$5:$G$22))</f>
         <v>16</v>
       </c>
-      <c r="E30" s="17">
+      <c r="E30" s="9">
         <f>COUNTIFS($A$5:$A$22,A30,$H$5:$H$22,"High")</f>
         <v>1</v>
       </c>
-      <c r="F30" s="17">
+      <c r="F30" s="9">
         <f>COUNTIFS($A$5:$A$22,A30,$D$5:$D$22,"Threat")</f>
         <v>1</v>
       </c>
-      <c r="G30" s="17">
+      <c r="G30" s="9">
         <f>COUNTIFS($A$5:$A$22,A30,$D$5:$D$22,"Opportunity")</f>
         <v>2</v>
       </c>
-      <c r="H30" s="17">
+      <c r="H30" s="9">
         <f>RANK(C30,$C$27:$C$32)</f>
         <v>3</v>
       </c>
@@ -2520,115 +2290,108 @@
           <t>Legal</t>
         </is>
       </c>
-      <c r="B31" s="14">
+      <c r="B31" s="9">
         <f>COUNTIF($A$5:$A$22,A31)</f>
         <v>3</v>
       </c>
-      <c r="C31" s="24">
+      <c r="C31" s="12">
         <f>AVERAGEIF($A$5:$A$22,A31,$G$5:$G$22)</f>
         <v>11.6666666666667</v>
       </c>
-      <c r="D31" s="14">
+      <c r="D31" s="9">
         <f>SUMPRODUCT(MAX(($A$5:$A$22=A31)*$G$5:$G$22))</f>
         <v>15</v>
       </c>
-      <c r="E31" s="14">
+      <c r="E31" s="9">
         <f>COUNTIFS($A$5:$A$22,A31,$H$5:$H$22,"High")</f>
         <v>0</v>
       </c>
-      <c r="F31" s="14">
+      <c r="F31" s="9">
         <f>COUNTIFS($A$5:$A$22,A31,$D$5:$D$22,"Threat")</f>
         <v>3</v>
       </c>
-      <c r="G31" s="14">
+      <c r="G31" s="9">
         <f>COUNTIFS($A$5:$A$22,A31,$D$5:$D$22,"Opportunity")</f>
         <v>0</v>
       </c>
-      <c r="H31" s="14">
+      <c r="H31" s="9">
         <f>RANK(C31,$C$27:$C$32)</f>
         <v>5</v>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Environmental</t>
         </is>
       </c>
-      <c r="B32" s="17">
+      <c r="B32" s="9">
         <f>COUNTIF($A$5:$A$22,A32)</f>
         <v>3</v>
       </c>
-      <c r="C32" s="25">
+      <c r="C32" s="12">
         <f>AVERAGEIF($A$5:$A$22,A32,$G$5:$G$22)</f>
         <v>9</v>
       </c>
-      <c r="D32" s="17">
+      <c r="D32" s="9">
         <f>SUMPRODUCT(MAX(($A$5:$A$22=A32)*$G$5:$G$22))</f>
         <v>12</v>
       </c>
-      <c r="E32" s="17">
+      <c r="E32" s="9">
         <f>COUNTIFS($A$5:$A$22,A32,$H$5:$H$22,"High")</f>
         <v>0</v>
       </c>
-      <c r="F32" s="17">
+      <c r="F32" s="9">
         <f>COUNTIFS($A$5:$A$22,A32,$D$5:$D$22,"Threat")</f>
         <v>2</v>
       </c>
-      <c r="G32" s="17">
+      <c r="G32" s="9">
         <f>COUNTIFS($A$5:$A$22,A32,$D$5:$D$22,"Opportunity")</f>
         <v>1</v>
       </c>
-      <c r="H32" s="17">
+      <c r="H32" s="9">
         <f>RANK(C32,$C$27:$C$32)</f>
         <v>6</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>All factors</t>
         </is>
       </c>
-      <c r="B33" s="23">
+      <c r="B33" s="10">
         <f>SUM(B27:B32)</f>
         <v>18</v>
       </c>
-      <c r="C33" s="22">
+      <c r="C33" s="12">
         <f>AVERAGE(G5:G22)</f>
         <v>14.2222222222222</v>
       </c>
-      <c r="D33" s="23">
+      <c r="D33" s="10">
         <f>MAX(G5:G22)</f>
         <v>25</v>
       </c>
-      <c r="E33" s="23">
+      <c r="E33" s="10">
         <f>SUM(E27:E32)</f>
         <v>6</v>
       </c>
-      <c r="F33" s="23">
+      <c r="F33" s="10">
         <f>SUM(F27:F32)</f>
         <v>12</v>
       </c>
-      <c r="G33" s="23">
+      <c r="G33" s="10">
         <f>SUM(G27:G32)</f>
         <v>6</v>
       </c>
-      <c r="H33" s="23" t="n"/>
-    </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="H33" s="10" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>Key findings</t>
         </is>
       </c>
-      <c r="B35" s="9" t="n"/>
-      <c r="C35" s="9" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="9" t="n"/>
-      <c r="F35" s="9" t="n"/>
-      <c r="G35" s="9" t="n"/>
-      <c r="H35" s="9" t="n"/>
     </row>
     <row r="36" ht="24" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
@@ -2636,21 +2399,21 @@
           <t>Finding</t>
         </is>
       </c>
-      <c r="B36" s="26" t="n"/>
+      <c r="B36" s="13" t="n"/>
       <c r="C36" s="3" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="D36" s="26" t="n"/>
-      <c r="E36" s="26" t="n"/>
-      <c r="F36" s="26" t="n"/>
-      <c r="G36" s="13" t="inlineStr">
+      <c r="D36" s="13" t="n"/>
+      <c r="E36" s="13" t="n"/>
+      <c r="F36" s="13" t="n"/>
+      <c r="G36" s="8" t="inlineStr">
         <is>
           <t>Excel functions</t>
         </is>
       </c>
-      <c r="H36" s="26" t="n"/>
+      <c r="H36" s="13" t="n"/>
     </row>
     <row r="37" ht="21" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
@@ -2658,41 +2421,41 @@
           <t>Most important factor</t>
         </is>
       </c>
-      <c r="B37" s="27" t="n"/>
+      <c r="B37" s="11" t="n"/>
       <c r="C37" s="5" t="str">
         <f>INDEX($A$27:$A$32,MATCH(MAX($C$27:$C$32),$C$27:$C$32,0))&amp;" (average score "&amp;TEXT(MAX($C$27:$C$32),"0.0")&amp;")"</f>
         <v>Economic (average score 20.7)</v>
       </c>
-      <c r="D37" s="27" t="n"/>
-      <c r="E37" s="27" t="n"/>
-      <c r="F37" s="27" t="n"/>
-      <c r="G37" s="28" t="inlineStr">
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="11" t="n"/>
+      <c r="F37" s="11" t="n"/>
+      <c r="G37" s="9" t="inlineStr">
         <is>
           <t>INDEX, MATCH, MAX</t>
         </is>
       </c>
-      <c r="H37" s="27" t="n"/>
+      <c r="H37" s="11" t="n"/>
     </row>
     <row r="38" ht="21" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Least important factor</t>
         </is>
       </c>
-      <c r="B38" s="29" t="n"/>
-      <c r="C38" s="7" t="str">
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="5" t="str">
         <f>INDEX($A$27:$A$32,MATCH(MIN($C$27:$C$32),$C$27:$C$32,0))&amp;" (average score "&amp;TEXT(MIN($C$27:$C$32),"0.0")&amp;")"</f>
         <v>Environmental (average score 9.0)</v>
       </c>
-      <c r="D38" s="29" t="n"/>
-      <c r="E38" s="29" t="n"/>
-      <c r="F38" s="29" t="n"/>
-      <c r="G38" s="30" t="inlineStr">
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="11" t="n"/>
+      <c r="F38" s="11" t="n"/>
+      <c r="G38" s="9" t="inlineStr">
         <is>
           <t>INDEX, MATCH, MIN</t>
         </is>
       </c>
-      <c r="H38" s="29" t="n"/>
+      <c r="H38" s="11" t="n"/>
     </row>
     <row r="39" ht="21" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
@@ -2700,41 +2463,41 @@
           <t>Highest-scoring issue</t>
         </is>
       </c>
-      <c r="B39" s="27" t="n"/>
+      <c r="B39" s="11" t="n"/>
       <c r="C39" s="5" t="str">
         <f>INDEX($B$5:$B$22,MATCH(MAX($G$5:$G$22),$G$5:$G$22,0))&amp;" (score "&amp;MAX($G$5:$G$22)&amp;" of 25)"</f>
         <v>Naira devaluation and FX shortages (score 25 of 25)</v>
       </c>
-      <c r="D39" s="27" t="n"/>
-      <c r="E39" s="27" t="n"/>
-      <c r="F39" s="27" t="n"/>
-      <c r="G39" s="28" t="inlineStr">
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="11" t="n"/>
+      <c r="F39" s="11" t="n"/>
+      <c r="G39" s="9" t="inlineStr">
         <is>
           <t>INDEX, MATCH, MAX</t>
         </is>
       </c>
-      <c r="H39" s="27" t="n"/>
+      <c r="H39" s="11" t="n"/>
     </row>
     <row r="40" ht="21" customHeight="1">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>High-priority issues</t>
         </is>
       </c>
-      <c r="B40" s="29" t="n"/>
-      <c r="C40" s="7" t="str">
+      <c r="B40" s="11" t="n"/>
+      <c r="C40" s="5" t="str">
         <f>COUNTIF($H$5:$H$22,"High")&amp;" of "&amp;COUNTA($A$5:$A$22)&amp;" issues"</f>
         <v>6 of 18 issues</v>
       </c>
-      <c r="D40" s="29" t="n"/>
-      <c r="E40" s="29" t="n"/>
-      <c r="F40" s="29" t="n"/>
-      <c r="G40" s="30" t="inlineStr">
+      <c r="D40" s="11" t="n"/>
+      <c r="E40" s="11" t="n"/>
+      <c r="F40" s="11" t="n"/>
+      <c r="G40" s="9" t="inlineStr">
         <is>
           <t>COUNTIF, COUNTA</t>
         </is>
       </c>
-      <c r="H40" s="29" t="n"/>
+      <c r="H40" s="11" t="n"/>
     </row>
     <row r="41" ht="21" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
@@ -2742,34 +2505,27 @@
           <t>Threats and opportunities</t>
         </is>
       </c>
-      <c r="B41" s="27" t="n"/>
+      <c r="B41" s="11" t="n"/>
       <c r="C41" s="5" t="str">
         <f>COUNTIF($D$5:$D$22,"Threat")&amp;" threats, "&amp;COUNTIF($D$5:$D$22,"Opportunity")&amp;" opportunities"</f>
         <v>12 threats, 6 opportunities</v>
       </c>
-      <c r="D41" s="27" t="n"/>
-      <c r="E41" s="27" t="n"/>
-      <c r="F41" s="27" t="n"/>
-      <c r="G41" s="28" t="inlineStr">
+      <c r="D41" s="11" t="n"/>
+      <c r="E41" s="11" t="n"/>
+      <c r="F41" s="11" t="n"/>
+      <c r="G41" s="9" t="inlineStr">
         <is>
           <t>COUNTIF</t>
         </is>
       </c>
-      <c r="H41" s="27" t="n"/>
-    </row>
-    <row r="43" ht="24" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="H41" s="11" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>Chart: average PESTLE score by factor</t>
         </is>
       </c>
-      <c r="B43" s="9" t="n"/>
-      <c r="C43" s="9" t="n"/>
-      <c r="D43" s="9" t="n"/>
-      <c r="E43" s="9" t="n"/>
-      <c r="F43" s="9" t="n"/>
-      <c r="G43" s="9" t="n"/>
-      <c r="H43" s="9" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1"/>
     <row r="45" ht="15" customHeight="1"/>
@@ -2816,16 +2572,8 @@
     <mergeCell ref="A39:B39"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;8 PZ Nigeria Limited - &amp;A - Page &amp;P of &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -2833,7 +2581,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001F3864"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2845,7 +2592,7 @@
     <col width="66" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
+    <row r="1" ht="21" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SWOT ANALYSIS: PZ NIGERIA LIMITED</t>
@@ -2859,201 +2606,200 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="8" customHeight="1"/>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="31" t="inlineStr"/>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="A4" s="14" t="n"/>
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>HELPFUL</t>
         </is>
       </c>
-      <c r="C4" s="32" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>HARMFUL</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="33" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
       </c>
-      <c r="B5" s="34" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>STRENGTHS</t>
         </is>
       </c>
-      <c r="C5" s="34" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>WEAKNESSES</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="35" t="n"/>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="A6" s="11" t="n"/>
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>1. Well-known brands such as Imperial Leather and Joy</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>1. Waiting for the UK owner's approval can slow work</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="35" t="n"/>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="A7" s="11" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>2. More than 100 years in Nigeria; trusted by buyers</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>2. Too many management levels can cause delays</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="35" t="n"/>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="A8" s="11" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>3. Wide distribution network across Nigeria</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>3. Brands may fight over the same marketing money</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="35" t="n"/>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="A9" s="11" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>4. Each business focuses on its own customers</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>4. Naira problems force hard decisions on imports</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="35" t="n"/>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="A10" s="11" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>5. One manager per brand; shared teams save money</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>5. Prices often higher than local low-cost brands</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="35" t="n"/>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="A11" s="11" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>6. Support from the UK owner (PZ Cussons)</t>
         </is>
       </c>
-      <c r="C11" s="11" t="n"/>
+      <c r="C11" s="5" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="33" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>EXTERNAL</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>OPPORTUNITIES</t>
         </is>
       </c>
-      <c r="C12" s="34" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>THREATS</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="35" t="n"/>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="A13" s="11" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>1. Large, young and growing population</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>1. Naira devaluation and foreign-exchange shortages</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="35" t="n"/>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="A14" s="11" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>2. Social media, e-commerce and modern retail</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>2. High inflation reduces what consumers can spend</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="35" t="n"/>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="A15" s="11" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>3. Smaller, affordable packs for shoppers on a budget</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>3. Strong competition and cheap imports</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="35" t="n"/>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="A16" s="11" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>4. Customers left by Unilever and P&amp;G since 2023</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>4. Fake (counterfeit) products</t>
         </is>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="35" t="n"/>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="A17" s="11" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>5. Exports to other African countries under AfCFTA</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>5. High energy and transport costs</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="35" t="n"/>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="A18" s="11" t="n"/>
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>6. Buying raw materials locally to cut dollar costs</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>6. Policy changes and insecurity</t>
         </is>
@@ -3065,8 +2811,8 @@
           <t>SWOT count</t>
         </is>
       </c>
-      <c r="B20" s="26" t="n"/>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>Number of points (COUNTA)</t>
         </is>
@@ -3078,20 +2824,20 @@
           <t>Strengths</t>
         </is>
       </c>
-      <c r="B21" s="27" t="n"/>
-      <c r="C21" s="14">
+      <c r="B21" s="11" t="n"/>
+      <c r="C21" s="9">
         <f>COUNTA(B6:B11)</f>
         <v>6</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Weaknesses</t>
         </is>
       </c>
-      <c r="B22" s="29" t="n"/>
-      <c r="C22" s="17">
+      <c r="B22" s="11" t="n"/>
+      <c r="C22" s="9">
         <f>COUNTA(C6:C11)</f>
         <v>5</v>
       </c>
@@ -3102,32 +2848,32 @@
           <t>Opportunities</t>
         </is>
       </c>
-      <c r="B23" s="27" t="n"/>
-      <c r="C23" s="14">
+      <c r="B23" s="11" t="n"/>
+      <c r="C23" s="9">
         <f>COUNTA(B13:B18)</f>
         <v>6</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Threats</t>
         </is>
       </c>
-      <c r="B24" s="29" t="n"/>
-      <c r="C24" s="17">
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="9">
         <f>COUNTA(C13:C18)</f>
         <v>6</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B25" s="21" t="n"/>
-      <c r="C25" s="23">
+      <c r="B25" s="11" t="n"/>
+      <c r="C25" s="10">
         <f>SUM(C21:C24)</f>
         <v>23</v>
       </c>
@@ -3146,23 +2892,14 @@
     <mergeCell ref="A5:A11"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;8 PZ Nigeria Limited - &amp;A - Page &amp;P of &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001F3864"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3176,7 +2913,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
+    <row r="1" ht="21" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SWOT SCORING: IFE AND EFE MATRICES</t>
@@ -3190,17 +2927,12 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="8" customHeight="1"/>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Internal Factor Evaluation (IFE): strengths and weaknesses</t>
         </is>
       </c>
-      <c r="B4" s="9" t="n"/>
-      <c r="C4" s="9" t="n"/>
-      <c r="D4" s="9" t="n"/>
-      <c r="E4" s="9" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -3213,17 +2945,17 @@
           <t>Key factor</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Weight</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Rating</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>Weighted score</t>
         </is>
@@ -3240,13 +2972,13 @@
           <t>Well-known brands such as Imperial Leather and Joy</t>
         </is>
       </c>
-      <c r="C6" s="36" t="n">
+      <c r="C6" s="16" t="n">
         <v>0.15</v>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E6" s="37">
+      <c r="E6" s="17">
         <f>C6*D6</f>
         <v>0.6</v>
       </c>
@@ -3262,13 +2994,13 @@
           <t>More than 100 years in Nigeria; trusted by buyers</t>
         </is>
       </c>
-      <c r="C7" s="36" t="n">
+      <c r="C7" s="16" t="n">
         <v>0.1</v>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="37">
+      <c r="E7" s="17">
         <f>C7*D7</f>
         <v>0.4</v>
       </c>
@@ -3284,13 +3016,13 @@
           <t>Wide distribution network across Nigeria</t>
         </is>
       </c>
-      <c r="C8" s="36" t="n">
+      <c r="C8" s="16" t="n">
         <v>0.12</v>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E8" s="37">
+      <c r="E8" s="17">
         <f>C8*D8</f>
         <v>0.36</v>
       </c>
@@ -3306,13 +3038,13 @@
           <t>Each business focuses on its own customers</t>
         </is>
       </c>
-      <c r="C9" s="36" t="n">
+      <c r="C9" s="16" t="n">
         <v>0.08</v>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="37">
+      <c r="E9" s="17">
         <f>C9*D9</f>
         <v>0.24</v>
       </c>
@@ -3328,13 +3060,13 @@
           <t>One manager per brand; shared teams save money</t>
         </is>
       </c>
-      <c r="C10" s="36" t="n">
+      <c r="C10" s="16" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E10" s="37">
+      <c r="E10" s="17">
         <f>C10*D10</f>
         <v>0.21</v>
       </c>
@@ -3350,182 +3082,178 @@
           <t>Support from the UK owner (PZ Cussons)</t>
         </is>
       </c>
-      <c r="C11" s="36" t="n">
+      <c r="C11" s="16" t="n">
         <v>0.08</v>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="37">
+      <c r="E11" s="17">
         <f>C11*D11</f>
         <v>0.24</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Weakness</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Waiting for the UK owner's approval can slow work</t>
         </is>
       </c>
-      <c r="C12" s="38" t="n">
+      <c r="C12" s="16" t="n">
         <v>0.08</v>
       </c>
-      <c r="D12" s="18" t="n">
+      <c r="D12" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="39">
+      <c r="E12" s="17">
         <f>C12*D12</f>
         <v>0.16</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Weakness</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Too many management levels can cause delays</t>
         </is>
       </c>
-      <c r="C13" s="38" t="n">
+      <c r="C13" s="16" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D13" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E13" s="39">
+      <c r="E13" s="17">
         <f>C13*D13</f>
         <v>0.14</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Weakness</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Brands may fight over the same marketing money</t>
         </is>
       </c>
-      <c r="C14" s="38" t="n">
+      <c r="C14" s="16" t="n">
         <v>0.05</v>
       </c>
-      <c r="D14" s="18" t="n">
+      <c r="D14" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E14" s="39">
+      <c r="E14" s="17">
         <f>C14*D14</f>
         <v>0.1</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Weakness</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Naira problems force hard decisions on imports</t>
         </is>
       </c>
-      <c r="C15" s="38" t="n">
+      <c r="C15" s="16" t="n">
         <v>0.12</v>
       </c>
-      <c r="D15" s="18" t="n">
+      <c r="D15" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="39">
+      <c r="E15" s="17">
         <f>C15*D15</f>
         <v>0.12</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Weakness</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Prices often higher than local low-cost brands</t>
         </is>
       </c>
-      <c r="C16" s="38" t="n">
+      <c r="C16" s="16" t="n">
         <v>0.08</v>
       </c>
-      <c r="D16" s="18" t="n">
+      <c r="D16" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E16" s="39">
+      <c r="E16" s="17">
         <f>C16*D16</f>
         <v>0.16</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B17" s="21" t="n"/>
-      <c r="C17" s="40">
+      <c r="B17" s="11" t="n"/>
+      <c r="C17" s="17">
         <f>SUM(C6:C16)</f>
         <v>1</v>
       </c>
-      <c r="D17" s="41" t="n"/>
-      <c r="E17" s="42">
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="17">
         <f>SUM(E6:E16)</f>
         <v>2.73</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Weights check</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n"/>
-      <c r="C18" s="11" t="str">
+      <c r="B18" s="11" t="n"/>
+      <c r="C18" s="5" t="str">
         <f>IF(ROUND(C17,2)=1,"OK: weights add up to 1.00","Check: weights must add up to 1.00")</f>
         <v>OK: weights add up to 1.00</v>
       </c>
-      <c r="D18" s="35" t="n"/>
-      <c r="E18" s="35" t="n"/>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="11" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="B19" s="35" t="n"/>
-      <c r="C19" s="10" t="str">
+      <c r="B19" s="11" t="n"/>
+      <c r="C19" s="4" t="str">
         <f>IF(E17&gt;=2.5,"Above average: strengths outweigh weaknesses","Below average: weaknesses outweigh strengths")</f>
         <v>Above average: strengths outweigh weaknesses</v>
       </c>
-      <c r="D19" s="35" t="n"/>
-      <c r="E19" s="35" t="n"/>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="11" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>External Factor Evaluation (EFE): opportunities and threats</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="9" t="n"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
@@ -3538,17 +3266,17 @@
           <t>Key factor</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>Weight</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>Rating</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>Weighted score</t>
         </is>
@@ -3565,13 +3293,13 @@
           <t>Large, young and growing population</t>
         </is>
       </c>
-      <c r="C23" s="36" t="n">
+      <c r="C23" s="16" t="n">
         <v>0.12</v>
       </c>
-      <c r="D23" s="15" t="n">
+      <c r="D23" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E23" s="37">
+      <c r="E23" s="17">
         <f>C23*D23</f>
         <v>0.36</v>
       </c>
@@ -3587,13 +3315,13 @@
           <t>Social media, e-commerce and modern retail</t>
         </is>
       </c>
-      <c r="C24" s="36" t="n">
+      <c r="C24" s="16" t="n">
         <v>0.08</v>
       </c>
-      <c r="D24" s="15" t="n">
+      <c r="D24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E24" s="37">
+      <c r="E24" s="17">
         <f>C24*D24</f>
         <v>0.16</v>
       </c>
@@ -3609,13 +3337,13 @@
           <t>Smaller, affordable packs for shoppers on a budget</t>
         </is>
       </c>
-      <c r="C25" s="36" t="n">
+      <c r="C25" s="16" t="n">
         <v>0.1</v>
       </c>
-      <c r="D25" s="15" t="n">
+      <c r="D25" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E25" s="37">
+      <c r="E25" s="17">
         <f>C25*D25</f>
         <v>0.3</v>
       </c>
@@ -3631,13 +3359,13 @@
           <t>Customers left by Unilever and P&amp;G since 2023</t>
         </is>
       </c>
-      <c r="C26" s="36" t="n">
+      <c r="C26" s="16" t="n">
         <v>0.1</v>
       </c>
-      <c r="D26" s="15" t="n">
+      <c r="D26" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E26" s="37">
+      <c r="E26" s="17">
         <f>C26*D26</f>
         <v>0.3</v>
       </c>
@@ -3653,13 +3381,13 @@
           <t>Exports to other African countries under AfCFTA</t>
         </is>
       </c>
-      <c r="C27" s="36" t="n">
+      <c r="C27" s="16" t="n">
         <v>0.04</v>
       </c>
-      <c r="D27" s="15" t="n">
+      <c r="D27" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E27" s="37">
+      <c r="E27" s="17">
         <f>C27*D27</f>
         <v>0.08</v>
       </c>
@@ -3675,204 +3403,200 @@
           <t>Buying raw materials locally to cut dollar costs</t>
         </is>
       </c>
-      <c r="C28" s="36" t="n">
+      <c r="C28" s="16" t="n">
         <v>0.06</v>
       </c>
-      <c r="D28" s="15" t="n">
+      <c r="D28" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E28" s="37">
+      <c r="E28" s="17">
         <f>C28*D28</f>
         <v>0.12</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Threat</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Naira devaluation and foreign-exchange shortages</t>
         </is>
       </c>
-      <c r="C29" s="38" t="n">
+      <c r="C29" s="16" t="n">
         <v>0.14</v>
       </c>
-      <c r="D29" s="18" t="n">
+      <c r="D29" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E29" s="39">
+      <c r="E29" s="17">
         <f>C29*D29</f>
         <v>0.28</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Threat</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>High inflation reduces what consumers can spend</t>
         </is>
       </c>
-      <c r="C30" s="38" t="n">
+      <c r="C30" s="16" t="n">
         <v>0.12</v>
       </c>
-      <c r="D30" s="18" t="n">
+      <c r="D30" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E30" s="39">
+      <c r="E30" s="17">
         <f>C30*D30</f>
         <v>0.24</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Threat</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Strong competition and cheap imports</t>
         </is>
       </c>
-      <c r="C31" s="38" t="n">
+      <c r="C31" s="16" t="n">
         <v>0.09</v>
       </c>
-      <c r="D31" s="18" t="n">
+      <c r="D31" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E31" s="39">
+      <c r="E31" s="17">
         <f>C31*D31</f>
         <v>0.27</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Threat</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Fake (counterfeit) products</t>
         </is>
       </c>
-      <c r="C32" s="38" t="n">
+      <c r="C32" s="16" t="n">
         <v>0.05</v>
       </c>
-      <c r="D32" s="18" t="n">
+      <c r="D32" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E32" s="39">
+      <c r="E32" s="17">
         <f>C32*D32</f>
         <v>0.1</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Threat</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>High energy and transport costs</t>
         </is>
       </c>
-      <c r="C33" s="38" t="n">
+      <c r="C33" s="16" t="n">
         <v>0.06</v>
       </c>
-      <c r="D33" s="18" t="n">
+      <c r="D33" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E33" s="39">
+      <c r="E33" s="17">
         <f>C33*D33</f>
         <v>0.12</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Threat</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Policy changes and insecurity</t>
         </is>
       </c>
-      <c r="C34" s="38" t="n">
+      <c r="C34" s="16" t="n">
         <v>0.04</v>
       </c>
-      <c r="D34" s="18" t="n">
+      <c r="D34" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E34" s="39">
+      <c r="E34" s="17">
         <f>C34*D34</f>
         <v>0.08</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="20" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B35" s="21" t="n"/>
-      <c r="C35" s="40">
+      <c r="B35" s="11" t="n"/>
+      <c r="C35" s="17">
         <f>SUM(C23:C34)</f>
         <v>1</v>
       </c>
-      <c r="D35" s="41" t="n"/>
-      <c r="E35" s="42">
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="17">
         <f>SUM(E23:E34)</f>
         <v>2.41</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Weights check</t>
         </is>
       </c>
-      <c r="B36" s="35" t="n"/>
-      <c r="C36" s="11" t="str">
+      <c r="B36" s="11" t="n"/>
+      <c r="C36" s="5" t="str">
         <f>IF(ROUND(C35,2)=1,"OK: weights add up to 1.00","Check: weights must add up to 1.00")</f>
         <v>OK: weights add up to 1.00</v>
       </c>
-      <c r="D36" s="35" t="n"/>
-      <c r="E36" s="35" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="11" t="n"/>
     </row>
     <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="B37" s="35" t="n"/>
-      <c r="C37" s="10" t="str">
+      <c r="B37" s="11" t="n"/>
+      <c r="C37" s="4" t="str">
         <f>IF(E35&gt;=2.5,"Above average: PZ responds well to opportunities and threats","Below average: PZ must respond better to opportunities and threats")</f>
         <v>Below average: PZ must respond better to opportunities and threats</v>
       </c>
-      <c r="D37" s="35" t="n"/>
-      <c r="E37" s="35" t="n"/>
-    </row>
-    <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="11" t="n"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>Strategic position</t>
         </is>
       </c>
-      <c r="B39" s="9" t="n"/>
-      <c r="C39" s="9" t="n"/>
-      <c r="D39" s="9" t="n"/>
-      <c r="E39" s="9" t="n"/>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
@@ -3880,14 +3604,14 @@
           <t>Measure</t>
         </is>
       </c>
-      <c r="B40" s="26" t="n"/>
-      <c r="C40" s="13" t="inlineStr">
+      <c r="B40" s="13" t="n"/>
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="D40" s="26" t="n"/>
-      <c r="E40" s="13" t="inlineStr">
+      <c r="D40" s="13" t="n"/>
+      <c r="E40" s="8" t="inlineStr">
         <is>
           <t>Excel functions</t>
         </is>
@@ -3899,31 +3623,31 @@
           <t>Strengths score</t>
         </is>
       </c>
-      <c r="B41" s="27" t="n"/>
-      <c r="C41" s="37">
+      <c r="B41" s="11" t="n"/>
+      <c r="C41" s="17">
         <f>SUMIF($A$6:$A$16,"Strength",$E$6:$E$16)</f>
         <v>2.05</v>
       </c>
-      <c r="D41" s="27" t="n"/>
-      <c r="E41" s="28" t="inlineStr">
+      <c r="D41" s="11" t="n"/>
+      <c r="E41" s="9" t="inlineStr">
         <is>
           <t>SUMIF</t>
         </is>
       </c>
     </row>
     <row r="42" ht="21" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Weaknesses score</t>
         </is>
       </c>
-      <c r="B42" s="29" t="n"/>
-      <c r="C42" s="39">
+      <c r="B42" s="11" t="n"/>
+      <c r="C42" s="17">
         <f>SUMIF($A$6:$A$16,"Weakness",$E$6:$E$16)</f>
         <v>0.68</v>
       </c>
-      <c r="D42" s="29" t="n"/>
-      <c r="E42" s="30" t="inlineStr">
+      <c r="D42" s="11" t="n"/>
+      <c r="E42" s="9" t="inlineStr">
         <is>
           <t>SUMIF</t>
         </is>
@@ -3935,31 +3659,31 @@
           <t>Opportunities score</t>
         </is>
       </c>
-      <c r="B43" s="27" t="n"/>
-      <c r="C43" s="37">
+      <c r="B43" s="11" t="n"/>
+      <c r="C43" s="17">
         <f>SUMIF($A$23:$A$34,"Opportunity",$E$23:$E$34)</f>
         <v>1.32</v>
       </c>
-      <c r="D43" s="27" t="n"/>
-      <c r="E43" s="28" t="inlineStr">
+      <c r="D43" s="11" t="n"/>
+      <c r="E43" s="9" t="inlineStr">
         <is>
           <t>SUMIF</t>
         </is>
       </c>
     </row>
     <row r="44" ht="21" customHeight="1">
-      <c r="A44" s="6" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>Threats score</t>
         </is>
       </c>
-      <c r="B44" s="29" t="n"/>
-      <c r="C44" s="39">
+      <c r="B44" s="11" t="n"/>
+      <c r="C44" s="17">
         <f>SUMIF($A$23:$A$34,"Threat",$E$23:$E$34)</f>
         <v>1.09</v>
       </c>
-      <c r="D44" s="29" t="n"/>
-      <c r="E44" s="30" t="inlineStr">
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="9" t="inlineStr">
         <is>
           <t>SUMIF</t>
         </is>
@@ -3971,31 +3695,31 @@
           <t>IFE total (internal)</t>
         </is>
       </c>
-      <c r="B45" s="27" t="n"/>
-      <c r="C45" s="37">
+      <c r="B45" s="11" t="n"/>
+      <c r="C45" s="17">
         <f>E17</f>
         <v>2.73</v>
       </c>
-      <c r="D45" s="27" t="n"/>
-      <c r="E45" s="28" t="inlineStr">
+      <c r="D45" s="11" t="n"/>
+      <c r="E45" s="9" t="inlineStr">
         <is>
           <t>SUM</t>
         </is>
       </c>
     </row>
     <row r="46" ht="21" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>EFE total (external)</t>
         </is>
       </c>
-      <c r="B46" s="29" t="n"/>
-      <c r="C46" s="39">
+      <c r="B46" s="11" t="n"/>
+      <c r="C46" s="17">
         <f>E35</f>
         <v>2.41</v>
       </c>
-      <c r="D46" s="29" t="n"/>
-      <c r="E46" s="30" t="inlineStr">
+      <c r="D46" s="11" t="n"/>
+      <c r="E46" s="9" t="inlineStr">
         <is>
           <t>SUM</t>
         </is>
@@ -4007,31 +3731,31 @@
           <t>IE matrix cell</t>
         </is>
       </c>
-      <c r="B47" s="27" t="n"/>
-      <c r="C47" s="16" t="str">
+      <c r="B47" s="11" t="n"/>
+      <c r="C47" s="10" t="str">
         <f>CHOOSE((IF(E35&gt;=3,1,IF(E35&gt;=2,2,3))-1)*3+IF(E17&gt;=3,1,IF(E17&gt;=2,2,3)),"I","II","III","IV","V","VI","VII","VIII","IX")</f>
         <v>V</v>
       </c>
-      <c r="D47" s="27" t="n"/>
-      <c r="E47" s="28" t="inlineStr">
+      <c r="D47" s="11" t="n"/>
+      <c r="E47" s="9" t="inlineStr">
         <is>
           <t>IF, CHOOSE</t>
         </is>
       </c>
     </row>
     <row r="48" ht="21" customHeight="1">
-      <c r="A48" s="6" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>Strategy</t>
         </is>
       </c>
-      <c r="B48" s="29" t="n"/>
-      <c r="C48" s="19" t="str">
+      <c r="B48" s="11" t="n"/>
+      <c r="C48" s="10" t="str">
         <f>CHOOSE((IF(E35&gt;=3,1,IF(E35&gt;=2,2,3))-1)*3+IF(E17&gt;=3,1,IF(E17&gt;=2,2,3)),"Grow and build","Grow and build","Hold and maintain","Grow and build","Hold and maintain","Harvest or divest","Hold and maintain","Harvest or divest","Harvest or divest")</f>
         <v>Hold and maintain</v>
       </c>
-      <c r="D48" s="29" t="n"/>
-      <c r="E48" s="30" t="inlineStr">
+      <c r="D48" s="11" t="n"/>
+      <c r="E48" s="9" t="inlineStr">
         <is>
           <t>IF, CHOOSE</t>
         </is>
@@ -4043,28 +3767,24 @@
           <t>Suggested strategies</t>
         </is>
       </c>
-      <c r="B49" s="27" t="n"/>
-      <c r="C49" s="16" t="str">
+      <c r="B49" s="11" t="n"/>
+      <c r="C49" s="10" t="str">
         <f>IF(C48="Hold and maintain","Market penetration and product development",IF(C48="Grow and build","Market penetration, market development and product development","Cut costs or sell weak businesses"))</f>
         <v>Market penetration and product development</v>
       </c>
-      <c r="D49" s="27" t="n"/>
-      <c r="E49" s="28" t="inlineStr">
+      <c r="D49" s="11" t="n"/>
+      <c r="E49" s="9" t="inlineStr">
         <is>
           <t>IF</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="24" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>Chart: weighted SWOT scores</t>
         </is>
       </c>
-      <c r="B51" s="9" t="n"/>
-      <c r="C51" s="9" t="n"/>
-      <c r="D51" s="9" t="n"/>
-      <c r="E51" s="9" t="n"/>
     </row>
     <row r="52" ht="15" customHeight="1"/>
     <row r="53" ht="15" customHeight="1"/>
@@ -4122,16 +3842,8 @@
     <mergeCell ref="C49:D49"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;8 PZ Nigeria Limited - &amp;A - Page &amp;P of &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -4139,7 +3851,6 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001F3864"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4152,7 +3863,7 @@
     <col width="62" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
+    <row r="1" ht="21" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>INDUSTRY ANALYSIS: NIGERIAN FMCG AND CONSUMER ELECTRICALS</t>
@@ -4166,16 +3877,12 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="8" customHeight="1"/>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Industry overview</t>
         </is>
       </c>
-      <c r="B4" s="9" t="n"/>
-      <c r="C4" s="9" t="n"/>
-      <c r="D4" s="9" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -4188,22 +3895,22 @@
           <t>Fast-moving consumer goods (FMCG): personal care (soaps, bathing) and home care (dishwashing), plus consumer electricals</t>
         </is>
       </c>
-      <c r="C5" s="27" t="n"/>
-      <c r="D5" s="27" t="n"/>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="11" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Over 200 million people, most of them young: one of Africa's largest consumer markets</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n"/>
-      <c r="D6" s="29" t="n"/>
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="11" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -4216,22 +3923,22 @@
           <t>Households, reached through distributors, wholesalers, open markets, supermarkets and online stores</t>
         </is>
       </c>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
+      <c r="C7" s="11" t="n"/>
+      <c r="D7" s="11" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Key trends</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Prices rising with inflation; shoppers moving to smaller packs and cheaper brands; multinationals cutting local production; more selling online and on social media</t>
         </is>
       </c>
-      <c r="C8" s="29" t="n"/>
-      <c r="D8" s="29" t="n"/>
+      <c r="C8" s="11" t="n"/>
+      <c r="D8" s="11" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -4244,18 +3951,15 @@
           <t>Strong brands, low costs, wide distribution, local raw materials and affordable pack sizes</t>
         </is>
       </c>
-      <c r="C9" s="27" t="n"/>
-      <c r="D9" s="27" t="n"/>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="C9" s="11" t="n"/>
+      <c r="D9" s="11" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Porter's Five Forces</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
@@ -4263,12 +3967,12 @@
           <t>Force</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Strength (1-5)</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
@@ -4285,10 +3989,10 @@
           <t>Competitive rivalry</t>
         </is>
       </c>
-      <c r="B13" s="15" t="n">
+      <c r="B13" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="C13" s="16" t="str">
+      <c r="C13" s="10" t="str">
         <f>IF(B13&gt;=4,"High",IF(B13&gt;=3,"Medium","Low"))</f>
         <v>High</v>
       </c>
@@ -4299,19 +4003,19 @@
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Bargaining power of buyers</t>
         </is>
       </c>
-      <c r="B14" s="18" t="n">
+      <c r="B14" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="C14" s="19" t="str">
+      <c r="C14" s="10" t="str">
         <f>IF(B14&gt;=4,"High",IF(B14&gt;=3,"Medium","Low"))</f>
         <v>High</v>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Shoppers are price-sensitive and switch brands easily; big distributors bargain hard</t>
         </is>
@@ -4323,10 +4027,10 @@
           <t>Bargaining power of suppliers</t>
         </is>
       </c>
-      <c r="B15" s="15" t="n">
+      <c r="B15" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="C15" s="16" t="str">
+      <c r="C15" s="10" t="str">
         <f>IF(B15&gt;=4,"High",IF(B15&gt;=3,"Medium","Low"))</f>
         <v>High</v>
       </c>
@@ -4337,19 +4041,19 @@
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Threat of substitutes</t>
         </is>
       </c>
-      <c r="B16" s="18" t="n">
+      <c r="B16" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="19" t="str">
+      <c r="C16" s="10" t="str">
         <f>IF(B16&gt;=4,"High",IF(B16&gt;=3,"Medium","Low"))</f>
         <v>Medium</v>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Cheaper unbranded and local soaps; fans instead of air conditioners</t>
         </is>
@@ -4361,10 +4065,10 @@
           <t>Threat of new entrants</t>
         </is>
       </c>
-      <c r="B17" s="15" t="n">
+      <c r="B17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="16" t="str">
+      <c r="C17" s="10" t="str">
         <f>IF(B17&gt;=4,"High",IF(B17&gt;=3,"Medium","Low"))</f>
         <v>Low</v>
       </c>
@@ -4375,72 +4079,69 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Average strength</t>
         </is>
       </c>
-      <c r="B18" s="22">
+      <c r="B18" s="12">
         <f>AVERAGE(B13:B17)</f>
         <v>3.6</v>
       </c>
-      <c r="C18" s="23" t="str">
+      <c r="C18" s="10" t="str">
         <f>IF(B18&gt;=3.5,"High",IF(B18&gt;=2.5,"Medium","Low"))</f>
         <v>High</v>
       </c>
-      <c r="D18" s="20" t="str">
+      <c r="D18" s="4" t="str">
         <f>IF(B18&gt;=3.5,"Strong competitive pressure: profits are hard to earn",IF(B18&gt;=2.5,"Moderate competitive pressure","Weak competitive pressure: an attractive industry"))</f>
         <v>Strong competitive pressure: profits are hard to earn</v>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Strongest force</t>
         </is>
       </c>
-      <c r="B19" s="11" t="str">
+      <c r="B19" s="5" t="str">
         <f>INDEX($A$13:$A$17,MATCH(MAX($B$13:$B$17),$B$13:$B$17,0))</f>
         <v>Competitive rivalry</v>
       </c>
-      <c r="C19" s="35" t="n"/>
-      <c r="D19" s="35" t="n"/>
+      <c r="C19" s="11" t="n"/>
+      <c r="D19" s="11" t="n"/>
     </row>
     <row r="20" ht="21" customHeight="1">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Weakest force</t>
         </is>
       </c>
-      <c r="B20" s="11" t="str">
+      <c r="B20" s="5" t="str">
         <f>INDEX($A$13:$A$17,MATCH(MIN($B$13:$B$17),$B$13:$B$17,0))</f>
         <v>Threat of new entrants</v>
       </c>
-      <c r="C20" s="35" t="n"/>
-      <c r="D20" s="35" t="n"/>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="11" t="n"/>
     </row>
     <row r="21" ht="21" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Forces rated High</t>
         </is>
       </c>
-      <c r="B21" s="11" t="str">
+      <c r="B21" s="5" t="str">
         <f>COUNTIF($C$13:$C$17,"High")&amp;" of "&amp;COUNTA($A$13:$A$17)</f>
         <v>3 of 5</v>
       </c>
-      <c r="C21" s="35" t="n"/>
-      <c r="D21" s="35" t="n"/>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="11" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Main competitors</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
@@ -4487,22 +4188,22 @@
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Procter &amp; Gamble</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Ariel, Pampers, Always</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Home care</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>Stopped making products in Nigeria; imports only (announced 2023)</t>
         </is>
@@ -4531,22 +4232,22 @@
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Hayat Kimya</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Molfix, Bingo, Familia</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Home care</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>Makes products locally; low prices; growing fast</t>
         </is>
@@ -4575,49 +4276,46 @@
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>LG, Samsung, Hisense, Scanfrost</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Air conditioners, fridges, washing machines</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Electrical</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Strong brands, plus many cheaper imports</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="20" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Number of competitors listed</t>
         </is>
       </c>
-      <c r="B31" s="20">
+      <c r="B31" s="4">
         <f>COUNTA(A25:A30)</f>
         <v>6</v>
       </c>
-      <c r="C31" s="21" t="n"/>
-      <c r="D31" s="21" t="n"/>
-    </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="11" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>Chart: strength of the five forces</t>
         </is>
       </c>
-      <c r="B33" s="9" t="n"/>
-      <c r="C33" s="9" t="n"/>
-      <c r="D33" s="9" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1"/>
     <row r="35" ht="15" customHeight="1"/>
@@ -4655,16 +4353,8 @@
     <mergeCell ref="B20:D20"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;8 PZ Nigeria Limited - &amp;A - Page &amp;P of &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -4672,7 +4362,6 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001F3864"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4683,7 +4372,7 @@
     <col width="92" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
+    <row r="1" ht="21" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SUMMARY AND RECOMMENDATIONS</t>
@@ -4697,7 +4386,6 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="8" customHeight="1"/>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -4722,12 +4410,12 @@
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>PESTLE: highest-scoring issue</t>
         </is>
       </c>
-      <c r="B6" s="7" t="str">
+      <c r="B6" s="5" t="str">
         <f>PESTLE!C39</f>
         <v>Naira devaluation and FX shortages (score 25 of 25)</v>
       </c>
@@ -4744,12 +4432,12 @@
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>SWOT: points listed</t>
         </is>
       </c>
-      <c r="B8" s="7" t="str">
+      <c r="B8" s="5" t="str">
         <f>SWOT!C25&amp;" (strengths "&amp;SWOT!C21&amp;", weaknesses "&amp;SWOT!C22&amp;", opportunities "&amp;SWOT!C23&amp;", threats "&amp;SWOT!C24&amp;")"</f>
         <v>23 (strengths 6, weaknesses 5, opportunities 6, threats 6)</v>
       </c>
@@ -4766,12 +4454,12 @@
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>EFE total (external response)</t>
         </is>
       </c>
-      <c r="B10" s="7" t="str">
+      <c r="B10" s="5" t="str">
         <f>TEXT('SWOT Scoring'!E35,"0.00")&amp;" out of 4. "&amp;'SWOT Scoring'!C37</f>
         <v>2.41 out of 4. Below average: PZ must respond better to opportunities and threats</v>
       </c>
@@ -4788,12 +4476,12 @@
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Five Forces: average strength</t>
         </is>
       </c>
-      <c r="B12" s="7" t="str">
+      <c r="B12" s="5" t="str">
         <f>TEXT('Industry Analysis'!B18,"0.0")&amp;" out of 5. "&amp;'Industry Analysis'!D18</f>
         <v>3.6 out of 5. Strong competitive pressure: profits are hard to earn</v>
       </c>
@@ -4809,13 +4497,12 @@
         <v>Competitive rivalry</v>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Recommendations</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n"/>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
@@ -4842,12 +4529,12 @@
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>2. Sell smaller, affordable packs</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Keeps price-sensitive shoppers buying Imperial Leather, Premier Cool, Joy and Morning Fresh</t>
         </is>
@@ -4866,12 +4553,12 @@
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>4. Win customers competitors left behind</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Use the wide distribution network to fill shelves Unilever and P&amp;G have left</t>
         </is>
@@ -4890,7 +4577,7 @@
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>Ratings and weights are the analyst's judgement, based on the company information and public news up to 2025. Check the latest figures (exchange rate, inflation) before presenting.</t>
         </is>
@@ -4904,15 +4591,7 @@
     <mergeCell ref="A15:B15"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;8 PZ Nigeria Limited - &amp;A - Page &amp;P of &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>
--- a/pz-analysis/PZ_Nigeria_Analysis.xlsx
+++ b/pz-analysis/PZ_Nigeria_Analysis.xlsx
@@ -24,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,7 +36,7 @@
       <name val="Calibri"/>
       <family val="2"/>
       <b val="1"/>
-      <color rgb="00000000"/>
+      <color theme="4" tint="-0.499984740745262"/>
       <sz val="14"/>
       <scheme val="minor"/>
     </font>
@@ -52,6 +52,14 @@
       <name val="Calibri"/>
       <family val="2"/>
       <b val="1"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
       <scheme val="minor"/>
@@ -60,12 +68,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <b val="1"/>
-      <color rgb="00000000"/>
+      <color theme="4" tint="-0.499984740745262"/>
       <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -74,8 +82,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
-        <bgColor rgb="00D9D9D9"/>
+        <fgColor theme="4" tint="-0.499984740745262"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
       </patternFill>
     </fill>
   </fills>
@@ -89,23 +101,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00000000"/>
+        <color theme="0" tint="-0.249977111117893"/>
       </left>
       <right style="thin">
-        <color rgb="00000000"/>
+        <color theme="0" tint="-0.249977111117893"/>
       </right>
       <top style="thin">
-        <color rgb="00000000"/>
+        <color theme="0" tint="-0.249977111117893"/>
       </top>
       <bottom style="thin">
-        <color rgb="00000000"/>
+        <color theme="0" tint="-0.249977111117893"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -116,13 +128,13 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -134,30 +146,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="5" tint="-0.249977111117893"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -269,13 +295,29 @@
           <order val="0"/>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="595959"/>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
               <f>'PESTLE'!$A$27:$A$32</f>
@@ -471,13 +513,43 @@
           <order val="0"/>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="595959"/>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
               <f>'SWOT Scoring'!$A$41:$A$44</f>
@@ -673,13 +745,29 @@
           <order val="0"/>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="595959"/>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="50000"/>
+              </a:schemeClr>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
               <f>'Industry Analysis'!$A$13:$A$17</f>
@@ -2571,6 +2659,11 @@
     <mergeCell ref="C36:F36"/>
     <mergeCell ref="A39:B39"/>
   </mergeCells>
+  <conditionalFormatting sqref="H5:H22">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"High"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2613,14 +2706,14 @@
           <t>HELPFUL</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>HARMFUL</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>INTERNAL</t>
         </is>
@@ -2630,7 +2723,7 @@
           <t>STRENGTHS</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>WEAKNESSES</t>
         </is>
@@ -2711,7 +2804,7 @@
       <c r="C11" s="5" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>EXTERNAL</t>
         </is>
@@ -2721,7 +2814,7 @@
           <t>OPPORTUNITIES</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>THREATS</t>
         </is>
@@ -2972,13 +3065,13 @@
           <t>Well-known brands such as Imperial Leather and Joy</t>
         </is>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="18" t="n">
         <v>0.15</v>
       </c>
       <c r="D6" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="19">
         <f>C6*D6</f>
         <v>0.6</v>
       </c>
@@ -2994,13 +3087,13 @@
           <t>More than 100 years in Nigeria; trusted by buyers</t>
         </is>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="18" t="n">
         <v>0.1</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="19">
         <f>C7*D7</f>
         <v>0.4</v>
       </c>
@@ -3016,13 +3109,13 @@
           <t>Wide distribution network across Nigeria</t>
         </is>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="18" t="n">
         <v>0.12</v>
       </c>
       <c r="D8" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="19">
         <f>C8*D8</f>
         <v>0.36</v>
       </c>
@@ -3038,13 +3131,13 @@
           <t>Each business focuses on its own customers</t>
         </is>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="18" t="n">
         <v>0.08</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="19">
         <f>C9*D9</f>
         <v>0.24</v>
       </c>
@@ -3060,13 +3153,13 @@
           <t>One manager per brand; shared teams save money</t>
         </is>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="18" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="D10" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="19">
         <f>C10*D10</f>
         <v>0.21</v>
       </c>
@@ -3082,13 +3175,13 @@
           <t>Support from the UK owner (PZ Cussons)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="18" t="n">
         <v>0.08</v>
       </c>
       <c r="D11" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="19">
         <f>C11*D11</f>
         <v>0.24</v>
       </c>
@@ -3104,13 +3197,13 @@
           <t>Waiting for the UK owner's approval can slow work</t>
         </is>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="18" t="n">
         <v>0.08</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="19">
         <f>C12*D12</f>
         <v>0.16</v>
       </c>
@@ -3126,13 +3219,13 @@
           <t>Too many management levels can cause delays</t>
         </is>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="18" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="D13" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="19">
         <f>C13*D13</f>
         <v>0.14</v>
       </c>
@@ -3148,13 +3241,13 @@
           <t>Brands may fight over the same marketing money</t>
         </is>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="18" t="n">
         <v>0.05</v>
       </c>
       <c r="D14" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="19">
         <f>C14*D14</f>
         <v>0.1</v>
       </c>
@@ -3170,13 +3263,13 @@
           <t>Naira problems force hard decisions on imports</t>
         </is>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="18" t="n">
         <v>0.12</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="19">
         <f>C15*D15</f>
         <v>0.12</v>
       </c>
@@ -3192,13 +3285,13 @@
           <t>Prices often higher than local low-cost brands</t>
         </is>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="18" t="n">
         <v>0.08</v>
       </c>
       <c r="D16" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="19">
         <f>C16*D16</f>
         <v>0.16</v>
       </c>
@@ -3210,12 +3303,12 @@
         </is>
       </c>
       <c r="B17" s="11" t="n"/>
-      <c r="C17" s="17">
+      <c r="C17" s="19">
         <f>SUM(C6:C16)</f>
         <v>1</v>
       </c>
       <c r="D17" s="5" t="n"/>
-      <c r="E17" s="17">
+      <c r="E17" s="19">
         <f>SUM(E6:E16)</f>
         <v>2.73</v>
       </c>
@@ -3293,13 +3386,13 @@
           <t>Large, young and growing population</t>
         </is>
       </c>
-      <c r="C23" s="16" t="n">
+      <c r="C23" s="18" t="n">
         <v>0.12</v>
       </c>
       <c r="D23" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="19">
         <f>C23*D23</f>
         <v>0.36</v>
       </c>
@@ -3315,13 +3408,13 @@
           <t>Social media, e-commerce and modern retail</t>
         </is>
       </c>
-      <c r="C24" s="16" t="n">
+      <c r="C24" s="18" t="n">
         <v>0.08</v>
       </c>
       <c r="D24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E24" s="17">
+      <c r="E24" s="19">
         <f>C24*D24</f>
         <v>0.16</v>
       </c>
@@ -3337,13 +3430,13 @@
           <t>Smaller, affordable packs for shoppers on a budget</t>
         </is>
       </c>
-      <c r="C25" s="16" t="n">
+      <c r="C25" s="18" t="n">
         <v>0.1</v>
       </c>
       <c r="D25" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E25" s="17">
+      <c r="E25" s="19">
         <f>C25*D25</f>
         <v>0.3</v>
       </c>
@@ -3359,13 +3452,13 @@
           <t>Customers left by Unilever and P&amp;G since 2023</t>
         </is>
       </c>
-      <c r="C26" s="16" t="n">
+      <c r="C26" s="18" t="n">
         <v>0.1</v>
       </c>
       <c r="D26" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E26" s="17">
+      <c r="E26" s="19">
         <f>C26*D26</f>
         <v>0.3</v>
       </c>
@@ -3381,13 +3474,13 @@
           <t>Exports to other African countries under AfCFTA</t>
         </is>
       </c>
-      <c r="C27" s="16" t="n">
+      <c r="C27" s="18" t="n">
         <v>0.04</v>
       </c>
       <c r="D27" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E27" s="17">
+      <c r="E27" s="19">
         <f>C27*D27</f>
         <v>0.08</v>
       </c>
@@ -3403,13 +3496,13 @@
           <t>Buying raw materials locally to cut dollar costs</t>
         </is>
       </c>
-      <c r="C28" s="16" t="n">
+      <c r="C28" s="18" t="n">
         <v>0.06</v>
       </c>
       <c r="D28" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E28" s="17">
+      <c r="E28" s="19">
         <f>C28*D28</f>
         <v>0.12</v>
       </c>
@@ -3425,13 +3518,13 @@
           <t>Naira devaluation and foreign-exchange shortages</t>
         </is>
       </c>
-      <c r="C29" s="16" t="n">
+      <c r="C29" s="18" t="n">
         <v>0.14</v>
       </c>
       <c r="D29" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E29" s="17">
+      <c r="E29" s="19">
         <f>C29*D29</f>
         <v>0.28</v>
       </c>
@@ -3447,13 +3540,13 @@
           <t>High inflation reduces what consumers can spend</t>
         </is>
       </c>
-      <c r="C30" s="16" t="n">
+      <c r="C30" s="18" t="n">
         <v>0.12</v>
       </c>
       <c r="D30" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E30" s="17">
+      <c r="E30" s="19">
         <f>C30*D30</f>
         <v>0.24</v>
       </c>
@@ -3469,13 +3562,13 @@
           <t>Strong competition and cheap imports</t>
         </is>
       </c>
-      <c r="C31" s="16" t="n">
+      <c r="C31" s="18" t="n">
         <v>0.09</v>
       </c>
       <c r="D31" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E31" s="17">
+      <c r="E31" s="19">
         <f>C31*D31</f>
         <v>0.27</v>
       </c>
@@ -3491,13 +3584,13 @@
           <t>Fake (counterfeit) products</t>
         </is>
       </c>
-      <c r="C32" s="16" t="n">
+      <c r="C32" s="18" t="n">
         <v>0.05</v>
       </c>
       <c r="D32" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E32" s="17">
+      <c r="E32" s="19">
         <f>C32*D32</f>
         <v>0.1</v>
       </c>
@@ -3513,13 +3606,13 @@
           <t>High energy and transport costs</t>
         </is>
       </c>
-      <c r="C33" s="16" t="n">
+      <c r="C33" s="18" t="n">
         <v>0.06</v>
       </c>
       <c r="D33" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E33" s="17">
+      <c r="E33" s="19">
         <f>C33*D33</f>
         <v>0.12</v>
       </c>
@@ -3535,13 +3628,13 @@
           <t>Policy changes and insecurity</t>
         </is>
       </c>
-      <c r="C34" s="16" t="n">
+      <c r="C34" s="18" t="n">
         <v>0.04</v>
       </c>
       <c r="D34" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E34" s="17">
+      <c r="E34" s="19">
         <f>C34*D34</f>
         <v>0.08</v>
       </c>
@@ -3553,12 +3646,12 @@
         </is>
       </c>
       <c r="B35" s="11" t="n"/>
-      <c r="C35" s="17">
+      <c r="C35" s="19">
         <f>SUM(C23:C34)</f>
         <v>1</v>
       </c>
       <c r="D35" s="5" t="n"/>
-      <c r="E35" s="17">
+      <c r="E35" s="19">
         <f>SUM(E23:E34)</f>
         <v>2.41</v>
       </c>
@@ -3624,7 +3717,7 @@
         </is>
       </c>
       <c r="B41" s="11" t="n"/>
-      <c r="C41" s="17">
+      <c r="C41" s="19">
         <f>SUMIF($A$6:$A$16,"Strength",$E$6:$E$16)</f>
         <v>2.05</v>
       </c>
@@ -3642,7 +3735,7 @@
         </is>
       </c>
       <c r="B42" s="11" t="n"/>
-      <c r="C42" s="17">
+      <c r="C42" s="19">
         <f>SUMIF($A$6:$A$16,"Weakness",$E$6:$E$16)</f>
         <v>0.68</v>
       </c>
@@ -3660,7 +3753,7 @@
         </is>
       </c>
       <c r="B43" s="11" t="n"/>
-      <c r="C43" s="17">
+      <c r="C43" s="19">
         <f>SUMIF($A$23:$A$34,"Opportunity",$E$23:$E$34)</f>
         <v>1.32</v>
       </c>
@@ -3678,7 +3771,7 @@
         </is>
       </c>
       <c r="B44" s="11" t="n"/>
-      <c r="C44" s="17">
+      <c r="C44" s="19">
         <f>SUMIF($A$23:$A$34,"Threat",$E$23:$E$34)</f>
         <v>1.09</v>
       </c>
@@ -3696,7 +3789,7 @@
         </is>
       </c>
       <c r="B45" s="11" t="n"/>
-      <c r="C45" s="17">
+      <c r="C45" s="19">
         <f>E17</f>
         <v>2.73</v>
       </c>
@@ -3714,7 +3807,7 @@
         </is>
       </c>
       <c r="B46" s="11" t="n"/>
-      <c r="C46" s="17">
+      <c r="C46" s="19">
         <f>E35</f>
         <v>2.41</v>
       </c>
@@ -4352,6 +4445,11 @@
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B20:D20"/>
   </mergeCells>
+  <conditionalFormatting sqref="C13:C17">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"High"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
